--- a/Mod_Korean/Lang/KR/Data/god_talk.xlsx
+++ b/Mod_Korean/Lang/KR/Data/god_talk.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="387">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t xml:space="preserve">…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umimya-!</t>
   </si>
   <si>
     <t xml:space="preserve">Welcome, welcome. I will ensure that you are never bored.</t>
@@ -775,6 +772,39 @@
   <si>
     <t xml:space="preserve">Are you going to my brother? Be a good little one, alright?
 Oh my, I hope my brother takes a liking to you…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A foolish institution. Very well, I shall celebrate it just for today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tying yourself down like that? How ridiculous, kitten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In my name, I bestow my blessing upon you both.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be happy! Happy!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muwahahahahaha!!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I-I'm not jealous or anything. ...stupid...congratulations...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Never let go...never...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You have my blessing. I shall refrain from mischief—just for today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oh my, how very delightful! Congratulations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I give you my congratulations. A fine achievement for your race.</t>
   </si>
   <si>
     <t xml:space="preserve">새로운 신도인가. 내 이름에 누가 되지 않도록 노력하도록.</t>
@@ -1533,7 +1563,7 @@
       <protection locked="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
       <alignment/>
       <protection locked="1"/>
@@ -1586,6 +1616,14 @@
       <alignment wrapText="1"/>
       <protection locked="1"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1610,9 +1648,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1341360</xdr:colOff>
+      <xdr:colOff>1340640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>154080</xdr:rowOff>
+      <xdr:rowOff>153360</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1622,7 +1660,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1341360" cy="154080"/>
+          <a:ext cx="1340640" cy="153360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1655,9 +1693,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1341360</xdr:colOff>
+      <xdr:colOff>1340640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>154800</xdr:rowOff>
+      <xdr:rowOff>154080</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1667,7 +1705,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1341360" cy="154800"/>
+          <a:ext cx="1340640" cy="154080"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
@@ -1697,9 +1735,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1172880</xdr:colOff>
+      <xdr:colOff>1172160</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>33480</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1709,7 +1747,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1172880" cy="358560"/>
+          <a:ext cx="1172160" cy="357840"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
@@ -1932,892 +1970,936 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>212</v>
+      <c r="J3" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="O3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="57.45">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>212</v>
+      <c r="J4" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="O4" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="23.85">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>212</v>
+      <c r="J5" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="O5" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="23.85">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>212</v>
+      <c r="K6" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="O6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="23.85">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>212</v>
+      <c r="J7" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="O7" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="23.85">
       <c r="A8" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>212</v>
+      <c r="J8" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O8" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="23.85">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>212</v>
+      <c r="J9" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="O9" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="23.85">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>212</v>
+      <c r="J10" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="O10" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="23.85">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>212</v>
+      <c r="J11" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="O11" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="35.05">
       <c r="A12" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>212</v>
+      <c r="J12" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="O12" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="57.45">
       <c r="A13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>212</v>
+      <c r="J13" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="O13" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="102.2">
       <c r="A14" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>212</v>
+      <c r="J14" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="O14" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" ht="91">
       <c r="A15" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>212</v>
+      <c r="J15" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="O15" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" ht="35.05">
       <c r="A16" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>212</v>
+      <c r="J16" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="O16" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" ht="35.05">
       <c r="A17" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>212</v>
+      <c r="J17" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="O17" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" ht="23.85">
       <c r="A18" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>212</v>
+      <c r="J18" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="O18" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" ht="12.75">
       <c r="A19" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>212</v>
+      <c r="J19" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" ht="12.75">
       <c r="A20" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="O20" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="21" ht="32.8">
+      <c r="A21" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="O21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" ht="12.75">
+      <c r="A22" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="K20" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O20" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" ht="22.35">
-      <c r="A21" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O21" t="s">
-        <v>216</v>
+      <c r="M22" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="1048576" ht="12.8"/>
